--- a/data/attendance/ANNEX_FORMATION_Formation_Anglais_-_Let's_Go_04.xlsx
+++ b/data/attendance/ANNEX_FORMATION_Formation_Anglais_-_Let's_Go_04.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACF3C212-FA05-421A-857F-C46F8326FBB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7216948A-1F24-4860-8B6D-E78BC5BE2B96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="16080" windowWidth="29040" windowHeight="8490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Présences" sheetId="1" r:id="rId1"/>
@@ -740,7 +740,7 @@
         <v>46297</v>
       </c>
       <c r="D4" s="14">
-        <v>47394</v>
+        <v>46298</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>6</v>
@@ -997,7 +997,7 @@
         <v>0</v>
       </c>
       <c r="O8" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" s="9">
         <v>0</v>
